--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,6 +3043,131 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121391816</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41 vägförgrening 300–340 m N, grustag NV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>703987</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6361209</v>
+      </c>
+      <c r="S22" t="n">
+        <v>31</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>I-Got-1581</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 träd/plantor med koordinater 1655601 6360972 (6 m, 1,8 m, 2,3 m), 1655627 6360972 (6 plantor 0,3–0,6 m), 1655614 6360974 (1,8 m + 1,6 m), 1655605 6360983 (5,5 + 2 m), 1655606 6361001 (1,7 m), 1655626 6361014 (2,3 m)</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Gun Ingmansson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376331</v>
+        <v>121376330</v>
       </c>
       <c r="B12" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376325</v>
+        <v>121376317</v>
       </c>
       <c r="B13" t="n">
-        <v>102286</v>
+        <v>108965</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,55 +2004,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703973</v>
+        <v>704098</v>
       </c>
       <c r="R13" t="n">
-        <v>6361219</v>
+        <v>6361295</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2082,11 +2068,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376320</v>
+        <v>121376263</v>
       </c>
       <c r="B14" t="n">
-        <v>108955</v>
+        <v>102296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,41 +2111,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>704027</v>
+        <v>703994</v>
       </c>
       <c r="R14" t="n">
-        <v>6361257</v>
+        <v>6361190</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,6 +2189,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376327</v>
+        <v>121376328</v>
       </c>
       <c r="B15" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2268,21 +2268,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703972</v>
+        <v>703968</v>
       </c>
       <c r="R15" t="n">
-        <v>6361201</v>
+        <v>6361190</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2319,7 +2314,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2351,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376328</v>
+        <v>121376325</v>
       </c>
       <c r="B16" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2386,7 +2381,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2394,16 +2389,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703968</v>
+        <v>703973</v>
       </c>
       <c r="R16" t="n">
-        <v>6361190</v>
+        <v>6361219</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376317</v>
+        <v>121376313</v>
       </c>
       <c r="B17" t="n">
-        <v>108955</v>
+        <v>108965</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704098</v>
+        <v>704129</v>
       </c>
       <c r="R17" t="n">
-        <v>6361295</v>
+        <v>6361185</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376323</v>
+        <v>121376315</v>
       </c>
       <c r="B18" t="n">
-        <v>102286</v>
+        <v>108965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,55 +2591,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703993</v>
+        <v>704108</v>
       </c>
       <c r="R18" t="n">
-        <v>6361232</v>
+        <v>6361297</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2669,11 +2655,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376264</v>
+        <v>121376323</v>
       </c>
       <c r="B19" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2740,7 +2721,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2750,7 +2731,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2759,10 +2740,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703994</v>
+        <v>703993</v>
       </c>
       <c r="R19" t="n">
-        <v>6361190</v>
+        <v>6361232</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2799,7 +2780,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376313</v>
+        <v>121376320</v>
       </c>
       <c r="B20" t="n">
-        <v>108955</v>
+        <v>108965</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,10 +2852,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704129</v>
+        <v>704027</v>
       </c>
       <c r="R20" t="n">
-        <v>6361185</v>
+        <v>6361257</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2938,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376315</v>
+        <v>121376327</v>
       </c>
       <c r="B21" t="n">
-        <v>108955</v>
+        <v>102296</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,41 +2931,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704108</v>
+        <v>703972</v>
       </c>
       <c r="R21" t="n">
-        <v>6361297</v>
+        <v>6361201</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,6 +3009,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376330</v>
+        <v>121376320</v>
       </c>
       <c r="B12" t="n">
-        <v>102296</v>
+        <v>108965</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,55 +1878,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703981</v>
+        <v>704027</v>
       </c>
       <c r="R12" t="n">
-        <v>6361192</v>
+        <v>6361257</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,11 +1942,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376317</v>
+        <v>121376325</v>
       </c>
       <c r="B13" t="n">
-        <v>108965</v>
+        <v>102296</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,41 +1985,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704098</v>
+        <v>703973</v>
       </c>
       <c r="R13" t="n">
-        <v>6361295</v>
+        <v>6361219</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,6 +2063,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,7 +2099,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376263</v>
+        <v>121376327</v>
       </c>
       <c r="B14" t="n">
         <v>102296</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703994</v>
+        <v>703972</v>
       </c>
       <c r="R14" t="n">
-        <v>6361190</v>
+        <v>6361201</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0,6 m hög.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2346,7 +2346,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376325</v>
+        <v>121376330</v>
       </c>
       <c r="B16" t="n">
         <v>102296</v>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703973</v>
+        <v>703981</v>
       </c>
       <c r="R16" t="n">
-        <v>6361219</v>
+        <v>6361192</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376313</v>
+        <v>121376263</v>
       </c>
       <c r="B17" t="n">
-        <v>108965</v>
+        <v>102296</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,41 +2484,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704129</v>
+        <v>703994</v>
       </c>
       <c r="R17" t="n">
-        <v>6361185</v>
+        <v>6361190</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,6 +2562,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2686,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376323</v>
+        <v>121376313</v>
       </c>
       <c r="B19" t="n">
-        <v>102296</v>
+        <v>108965</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,55 +2717,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703993</v>
+        <v>704129</v>
       </c>
       <c r="R19" t="n">
-        <v>6361232</v>
+        <v>6361185</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2776,11 +2781,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376320</v>
+        <v>121376323</v>
       </c>
       <c r="B20" t="n">
-        <v>108965</v>
+        <v>102296</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,41 +2824,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704027</v>
+        <v>703993</v>
       </c>
       <c r="R20" t="n">
-        <v>6361257</v>
+        <v>6361232</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2888,6 +2902,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376327</v>
+        <v>121376317</v>
       </c>
       <c r="B21" t="n">
-        <v>102296</v>
+        <v>108965</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,55 +2950,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703972</v>
+        <v>704098</v>
       </c>
       <c r="R21" t="n">
-        <v>6361201</v>
+        <v>6361295</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,11 +3014,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376320</v>
+        <v>121376325</v>
       </c>
       <c r="B12" t="n">
-        <v>108965</v>
+        <v>102309</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,41 +1878,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704027</v>
+        <v>703973</v>
       </c>
       <c r="R12" t="n">
-        <v>6361257</v>
+        <v>6361219</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,6 +1956,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376325</v>
+        <v>121376264</v>
       </c>
       <c r="B13" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,7 +2027,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703973</v>
+        <v>703994</v>
       </c>
       <c r="R13" t="n">
-        <v>6361219</v>
+        <v>6361190</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2067,7 +2086,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,10 +2118,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376327</v>
+        <v>121376331</v>
       </c>
       <c r="B14" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,7 +2153,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2153,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703972</v>
+        <v>703981</v>
       </c>
       <c r="R14" t="n">
-        <v>6361201</v>
+        <v>6361192</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2193,7 +2212,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,7 +2247,7 @@
         <v>121376328</v>
       </c>
       <c r="B15" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2346,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376330</v>
+        <v>121376327</v>
       </c>
       <c r="B16" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2381,7 +2400,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2391,7 +2410,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2400,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703981</v>
+        <v>703972</v>
       </c>
       <c r="R16" t="n">
-        <v>6361192</v>
+        <v>6361201</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2440,7 +2459,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376263</v>
+        <v>121376313</v>
       </c>
       <c r="B17" t="n">
-        <v>102296</v>
+        <v>108978</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,55 +2503,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703994</v>
+        <v>704129</v>
       </c>
       <c r="R17" t="n">
-        <v>6361190</v>
+        <v>6361185</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2562,11 +2567,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376315</v>
+        <v>121376320</v>
       </c>
       <c r="B18" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704108</v>
+        <v>704027</v>
       </c>
       <c r="R18" t="n">
-        <v>6361297</v>
+        <v>6361257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376313</v>
+        <v>121376317</v>
       </c>
       <c r="B19" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704129</v>
+        <v>704098</v>
       </c>
       <c r="R19" t="n">
-        <v>6361185</v>
+        <v>6361295</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2815,7 +2815,7 @@
         <v>121376323</v>
       </c>
       <c r="B20" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376317</v>
+        <v>121376315</v>
       </c>
       <c r="B21" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704098</v>
+        <v>704108</v>
       </c>
       <c r="R21" t="n">
-        <v>6361295</v>
+        <v>6361297</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376325</v>
+        <v>121376315</v>
       </c>
       <c r="B12" t="n">
-        <v>102309</v>
+        <v>108979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,55 +1878,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703973</v>
+        <v>704108</v>
       </c>
       <c r="R12" t="n">
-        <v>6361219</v>
+        <v>6361297</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,11 +1942,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376264</v>
+        <v>121376320</v>
       </c>
       <c r="B13" t="n">
-        <v>102309</v>
+        <v>108979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,55 +1985,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703994</v>
+        <v>704027</v>
       </c>
       <c r="R13" t="n">
-        <v>6361190</v>
+        <v>6361257</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2082,11 +2049,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,10 +2080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376331</v>
+        <v>121376313</v>
       </c>
       <c r="B14" t="n">
-        <v>102309</v>
+        <v>108979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,55 +2092,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703981</v>
+        <v>704129</v>
       </c>
       <c r="R14" t="n">
-        <v>6361192</v>
+        <v>6361185</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2208,11 +2156,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,7 +2190,7 @@
         <v>121376328</v>
       </c>
       <c r="B15" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376327</v>
+        <v>121376331</v>
       </c>
       <c r="B16" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,7 +2343,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2419,10 +2362,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703972</v>
+        <v>703981</v>
       </c>
       <c r="R16" t="n">
-        <v>6361201</v>
+        <v>6361192</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2459,7 +2402,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376313</v>
+        <v>121376264</v>
       </c>
       <c r="B17" t="n">
-        <v>108978</v>
+        <v>102310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2503,41 +2446,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704129</v>
+        <v>703994</v>
       </c>
       <c r="R17" t="n">
-        <v>6361185</v>
+        <v>6361190</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,6 +2524,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376320</v>
+        <v>121376323</v>
       </c>
       <c r="B18" t="n">
-        <v>108978</v>
+        <v>102310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,41 +2572,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704027</v>
+        <v>703993</v>
       </c>
       <c r="R18" t="n">
-        <v>6361257</v>
+        <v>6361232</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2674,6 +2650,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,7 +2689,7 @@
         <v>121376317</v>
       </c>
       <c r="B19" t="n">
-        <v>108978</v>
+        <v>108979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2812,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376323</v>
+        <v>121376325</v>
       </c>
       <c r="B20" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2857,7 +2838,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2866,10 +2847,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703993</v>
+        <v>703973</v>
       </c>
       <c r="R20" t="n">
-        <v>6361232</v>
+        <v>6361219</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2906,7 +2887,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376315</v>
+        <v>121376327</v>
       </c>
       <c r="B21" t="n">
-        <v>108978</v>
+        <v>102310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,41 +2931,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704108</v>
+        <v>703972</v>
       </c>
       <c r="R21" t="n">
-        <v>6361297</v>
+        <v>6361201</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,6 +3009,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376315</v>
+        <v>121376264</v>
       </c>
       <c r="B12" t="n">
-        <v>108979</v>
+        <v>102313</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,41 +1878,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704108</v>
+        <v>703994</v>
       </c>
       <c r="R12" t="n">
-        <v>6361297</v>
+        <v>6361190</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,6 +1956,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,7 +1995,7 @@
         <v>121376320</v>
       </c>
       <c r="B13" t="n">
-        <v>108979</v>
+        <v>108982</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2083,7 +2102,7 @@
         <v>121376313</v>
       </c>
       <c r="B14" t="n">
-        <v>108979</v>
+        <v>108982</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,10 +2206,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376328</v>
+        <v>121376317</v>
       </c>
       <c r="B15" t="n">
-        <v>102310</v>
+        <v>108982</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,50 +2218,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703968</v>
+        <v>704098</v>
       </c>
       <c r="R15" t="n">
-        <v>6361190</v>
+        <v>6361295</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,11 +2282,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376331</v>
+        <v>121376325</v>
       </c>
       <c r="B16" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,7 +2358,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703981</v>
+        <v>703973</v>
       </c>
       <c r="R16" t="n">
-        <v>6361192</v>
+        <v>6361219</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2402,7 +2407,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,10 +2439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376264</v>
+        <v>121376330</v>
       </c>
       <c r="B17" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2488,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703994</v>
+        <v>703981</v>
       </c>
       <c r="R17" t="n">
-        <v>6361190</v>
+        <v>6361192</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2528,7 +2533,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,7 +2568,7 @@
         <v>121376323</v>
       </c>
       <c r="B18" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2686,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376317</v>
+        <v>121376328</v>
       </c>
       <c r="B19" t="n">
-        <v>108979</v>
+        <v>102313</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,41 +2703,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704098</v>
+        <v>703968</v>
       </c>
       <c r="R19" t="n">
-        <v>6361295</v>
+        <v>6361190</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,6 +2776,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376325</v>
+        <v>121376327</v>
       </c>
       <c r="B20" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,7 +2847,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2838,7 +2857,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2847,10 +2866,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703973</v>
+        <v>703972</v>
       </c>
       <c r="R20" t="n">
-        <v>6361219</v>
+        <v>6361201</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2887,7 +2906,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376327</v>
+        <v>121376315</v>
       </c>
       <c r="B21" t="n">
-        <v>102310</v>
+        <v>108982</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,55 +2950,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703972</v>
+        <v>704108</v>
       </c>
       <c r="R21" t="n">
-        <v>6361201</v>
+        <v>6361297</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,11 +3014,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376264</v>
+        <v>121376331</v>
       </c>
       <c r="B12" t="n">
         <v>102313</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703994</v>
+        <v>703981</v>
       </c>
       <c r="R12" t="n">
-        <v>6361190</v>
+        <v>6361192</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376320</v>
+        <v>121376315</v>
       </c>
       <c r="B13" t="n">
         <v>108982</v>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704027</v>
+        <v>704108</v>
       </c>
       <c r="R13" t="n">
-        <v>6361257</v>
+        <v>6361297</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376317</v>
+        <v>121376264</v>
       </c>
       <c r="B15" t="n">
-        <v>108982</v>
+        <v>102313</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,41 +2218,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>704098</v>
+        <v>703994</v>
       </c>
       <c r="R15" t="n">
-        <v>6361295</v>
+        <v>6361190</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2282,6 +2296,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376325</v>
+        <v>121376317</v>
       </c>
       <c r="B16" t="n">
-        <v>102313</v>
+        <v>108982</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,55 +2344,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703973</v>
+        <v>704098</v>
       </c>
       <c r="R16" t="n">
-        <v>6361219</v>
+        <v>6361295</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2403,11 +2408,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,7 +2439,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376330</v>
+        <v>121376328</v>
       </c>
       <c r="B17" t="n">
         <v>102313</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,21 +2482,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703981</v>
+        <v>703968</v>
       </c>
       <c r="R17" t="n">
-        <v>6361192</v>
+        <v>6361190</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2533,7 +2528,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376323</v>
+        <v>121376320</v>
       </c>
       <c r="B18" t="n">
-        <v>102313</v>
+        <v>108982</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,55 +2572,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703993</v>
+        <v>704027</v>
       </c>
       <c r="R18" t="n">
-        <v>6361232</v>
+        <v>6361257</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2655,11 +2636,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2691,7 +2667,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376328</v>
+        <v>121376327</v>
       </c>
       <c r="B19" t="n">
         <v>102313</v>
@@ -2726,7 +2702,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2734,16 +2710,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703968</v>
+        <v>703972</v>
       </c>
       <c r="R19" t="n">
-        <v>6361190</v>
+        <v>6361201</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2780,7 +2761,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,7 +2793,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376327</v>
+        <v>121376325</v>
       </c>
       <c r="B20" t="n">
         <v>102313</v>
@@ -2847,7 +2828,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2857,7 +2838,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2866,10 +2847,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703972</v>
+        <v>703973</v>
       </c>
       <c r="R20" t="n">
-        <v>6361201</v>
+        <v>6361219</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2906,7 +2887,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376315</v>
+        <v>121376323</v>
       </c>
       <c r="B21" t="n">
-        <v>108982</v>
+        <v>102313</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,41 +2931,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704108</v>
+        <v>703993</v>
       </c>
       <c r="R21" t="n">
-        <v>6361297</v>
+        <v>6361232</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,6 +3009,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376331</v>
+        <v>121376263</v>
       </c>
       <c r="B12" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703981</v>
+        <v>703994</v>
       </c>
       <c r="R12" t="n">
-        <v>6361192</v>
+        <v>6361190</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376315</v>
+        <v>121376327</v>
       </c>
       <c r="B13" t="n">
-        <v>108982</v>
+        <v>102319</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,41 +2004,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704108</v>
+        <v>703972</v>
       </c>
       <c r="R13" t="n">
-        <v>6361297</v>
+        <v>6361201</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,6 +2082,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,7 +2121,7 @@
         <v>121376313</v>
       </c>
       <c r="B14" t="n">
-        <v>108982</v>
+        <v>108988</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2206,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376264</v>
+        <v>121376328</v>
       </c>
       <c r="B15" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,7 +2260,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2249,18 +2268,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703994</v>
+        <v>703968</v>
       </c>
       <c r="R15" t="n">
         <v>6361190</v>
@@ -2300,7 +2314,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376317</v>
+        <v>121376325</v>
       </c>
       <c r="B16" t="n">
-        <v>108982</v>
+        <v>102319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,41 +2358,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>704098</v>
+        <v>703973</v>
       </c>
       <c r="R16" t="n">
-        <v>6361295</v>
+        <v>6361219</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2408,6 +2436,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,10 +2472,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376328</v>
+        <v>121376331</v>
       </c>
       <c r="B17" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,7 +2507,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,16 +2515,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703968</v>
+        <v>703981</v>
       </c>
       <c r="R17" t="n">
-        <v>6361190</v>
+        <v>6361192</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2528,7 +2566,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,10 +2598,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376320</v>
+        <v>121376315</v>
       </c>
       <c r="B18" t="n">
-        <v>108982</v>
+        <v>108988</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2600,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704027</v>
+        <v>704108</v>
       </c>
       <c r="R18" t="n">
-        <v>6361257</v>
+        <v>6361297</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2667,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376327</v>
+        <v>121376317</v>
       </c>
       <c r="B19" t="n">
-        <v>102313</v>
+        <v>108988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,55 +2717,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703972</v>
+        <v>704098</v>
       </c>
       <c r="R19" t="n">
-        <v>6361201</v>
+        <v>6361295</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2757,11 +2781,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376325</v>
+        <v>121376323</v>
       </c>
       <c r="B20" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2838,7 +2857,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2847,10 +2866,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703973</v>
+        <v>703993</v>
       </c>
       <c r="R20" t="n">
-        <v>6361219</v>
+        <v>6361232</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2887,7 +2906,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376323</v>
+        <v>121376320</v>
       </c>
       <c r="B21" t="n">
-        <v>102313</v>
+        <v>108988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,55 +2950,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703993</v>
+        <v>704027</v>
       </c>
       <c r="R21" t="n">
-        <v>6361232</v>
+        <v>6361257</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,11 +3014,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376263</v>
+        <v>121376320</v>
       </c>
       <c r="B12" t="n">
-        <v>102319</v>
+        <v>108989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,55 +1878,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703994</v>
+        <v>704027</v>
       </c>
       <c r="R12" t="n">
-        <v>6361190</v>
+        <v>6361257</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,11 +1942,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,7 +1976,7 @@
         <v>121376327</v>
       </c>
       <c r="B13" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2118,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376313</v>
+        <v>121376331</v>
       </c>
       <c r="B14" t="n">
-        <v>108988</v>
+        <v>102320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,41 +2111,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>704129</v>
+        <v>703981</v>
       </c>
       <c r="R14" t="n">
-        <v>6361185</v>
+        <v>6361192</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,6 +2189,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376328</v>
+        <v>121376315</v>
       </c>
       <c r="B15" t="n">
-        <v>102319</v>
+        <v>108989</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,50 +2237,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703968</v>
+        <v>704108</v>
       </c>
       <c r="R15" t="n">
-        <v>6361190</v>
+        <v>6361297</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2310,11 +2301,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376325</v>
+        <v>121376317</v>
       </c>
       <c r="B16" t="n">
-        <v>102319</v>
+        <v>108989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,55 +2344,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703973</v>
+        <v>704098</v>
       </c>
       <c r="R16" t="n">
-        <v>6361219</v>
+        <v>6361295</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2436,11 +2408,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376331</v>
+        <v>121376313</v>
       </c>
       <c r="B17" t="n">
-        <v>102319</v>
+        <v>108989</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,55 +2451,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703981</v>
+        <v>704129</v>
       </c>
       <c r="R17" t="n">
-        <v>6361192</v>
+        <v>6361185</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2562,11 +2515,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,10 +2546,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376315</v>
+        <v>121376323</v>
       </c>
       <c r="B18" t="n">
-        <v>108988</v>
+        <v>102320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,41 +2558,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704108</v>
+        <v>703993</v>
       </c>
       <c r="R18" t="n">
-        <v>6361297</v>
+        <v>6361232</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2674,6 +2636,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376317</v>
+        <v>121376264</v>
       </c>
       <c r="B19" t="n">
-        <v>108988</v>
+        <v>102320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,41 +2684,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704098</v>
+        <v>703994</v>
       </c>
       <c r="R19" t="n">
-        <v>6361295</v>
+        <v>6361190</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2781,6 +2762,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2798,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376323</v>
+        <v>121376328</v>
       </c>
       <c r="B20" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2847,7 +2833,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2855,21 +2841,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703993</v>
+        <v>703968</v>
       </c>
       <c r="R20" t="n">
-        <v>6361232</v>
+        <v>6361190</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2906,7 +2887,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376320</v>
+        <v>121376325</v>
       </c>
       <c r="B21" t="n">
-        <v>108988</v>
+        <v>102320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,41 +2931,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704027</v>
+        <v>703973</v>
       </c>
       <c r="R21" t="n">
-        <v>6361257</v>
+        <v>6361219</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,6 +3009,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376320</v>
+        <v>121376331</v>
       </c>
       <c r="B12" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,41 +1878,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704027</v>
+        <v>703981</v>
       </c>
       <c r="R12" t="n">
-        <v>6361257</v>
+        <v>6361192</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,6 +1956,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,7 +1992,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376327</v>
+        <v>121376328</v>
       </c>
       <c r="B13" t="n">
         <v>102320</v>
@@ -2008,7 +2027,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2016,21 +2035,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703972</v>
+        <v>703968</v>
       </c>
       <c r="R13" t="n">
-        <v>6361201</v>
+        <v>6361190</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2067,7 +2081,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,7 +2113,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376331</v>
+        <v>121376323</v>
       </c>
       <c r="B14" t="n">
         <v>102320</v>
@@ -2153,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703981</v>
+        <v>703993</v>
       </c>
       <c r="R14" t="n">
-        <v>6361192</v>
+        <v>6361232</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2193,7 +2207,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2239,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376315</v>
+        <v>121376325</v>
       </c>
       <c r="B15" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,41 +2251,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>704108</v>
+        <v>703973</v>
       </c>
       <c r="R15" t="n">
-        <v>6361297</v>
+        <v>6361219</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2301,6 +2329,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376317</v>
+        <v>121376263</v>
       </c>
       <c r="B16" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,41 +2377,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>704098</v>
+        <v>703994</v>
       </c>
       <c r="R16" t="n">
-        <v>6361295</v>
+        <v>6361190</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2408,6 +2455,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,7 +2491,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376313</v>
+        <v>121376317</v>
       </c>
       <c r="B17" t="n">
         <v>108989</v>
@@ -2479,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704129</v>
+        <v>704098</v>
       </c>
       <c r="R17" t="n">
-        <v>6361185</v>
+        <v>6361295</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2546,7 +2598,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376323</v>
+        <v>121376327</v>
       </c>
       <c r="B18" t="n">
         <v>102320</v>
@@ -2581,7 +2633,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2600,10 +2652,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703993</v>
+        <v>703972</v>
       </c>
       <c r="R18" t="n">
-        <v>6361232</v>
+        <v>6361201</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2640,7 +2692,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376264</v>
+        <v>121376315</v>
       </c>
       <c r="B19" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,55 +2736,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703994</v>
+        <v>704108</v>
       </c>
       <c r="R19" t="n">
-        <v>6361190</v>
+        <v>6361297</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,11 +2800,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,10 +2831,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376328</v>
+        <v>121376313</v>
       </c>
       <c r="B20" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,50 +2843,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703968</v>
+        <v>704129</v>
       </c>
       <c r="R20" t="n">
-        <v>6361190</v>
+        <v>6361185</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2883,11 +2907,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376325</v>
+        <v>121376320</v>
       </c>
       <c r="B21" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,55 +2950,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703973</v>
+        <v>704027</v>
       </c>
       <c r="R21" t="n">
-        <v>6361219</v>
+        <v>6361257</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,11 +3014,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376331</v>
+        <v>121376325</v>
       </c>
       <c r="B12" t="n">
         <v>102320</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703981</v>
+        <v>703973</v>
       </c>
       <c r="R12" t="n">
-        <v>6361192</v>
+        <v>6361219</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376328</v>
+        <v>121376264</v>
       </c>
       <c r="B13" t="n">
         <v>102320</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2035,13 +2035,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703968</v>
+        <v>703994</v>
       </c>
       <c r="R13" t="n">
         <v>6361190</v>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,7 +2118,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376323</v>
+        <v>121376328</v>
       </c>
       <c r="B14" t="n">
         <v>102320</v>
@@ -2148,7 +2153,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2156,21 +2161,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703993</v>
+        <v>703968</v>
       </c>
       <c r="R14" t="n">
-        <v>6361232</v>
+        <v>6361190</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,7 +2239,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376325</v>
+        <v>121376327</v>
       </c>
       <c r="B15" t="n">
         <v>102320</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703973</v>
+        <v>703972</v>
       </c>
       <c r="R15" t="n">
-        <v>6361219</v>
+        <v>6361201</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376263</v>
+        <v>121376315</v>
       </c>
       <c r="B16" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2377,55 +2377,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703994</v>
+        <v>704108</v>
       </c>
       <c r="R16" t="n">
-        <v>6361190</v>
+        <v>6361297</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,11 +2441,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>0,6 m hög.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,7 +2472,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376317</v>
+        <v>121376313</v>
       </c>
       <c r="B17" t="n">
         <v>108989</v>
@@ -2531,10 +2512,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704098</v>
+        <v>704129</v>
       </c>
       <c r="R17" t="n">
-        <v>6361295</v>
+        <v>6361185</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2598,7 +2579,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376327</v>
+        <v>121376331</v>
       </c>
       <c r="B18" t="n">
         <v>102320</v>
@@ -2633,7 +2614,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2652,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703972</v>
+        <v>703981</v>
       </c>
       <c r="R18" t="n">
-        <v>6361201</v>
+        <v>6361192</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2692,7 +2673,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376315</v>
+        <v>121376323</v>
       </c>
       <c r="B19" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2736,41 +2717,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704108</v>
+        <v>703993</v>
       </c>
       <c r="R19" t="n">
-        <v>6361297</v>
+        <v>6361232</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,6 +2795,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,7 +2831,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376313</v>
+        <v>121376317</v>
       </c>
       <c r="B20" t="n">
         <v>108989</v>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704129</v>
+        <v>704098</v>
       </c>
       <c r="R20" t="n">
-        <v>6361185</v>
+        <v>6361295</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -1866,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376325</v>
+        <v>121376327</v>
       </c>
       <c r="B12" t="n">
         <v>102320</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703973</v>
+        <v>703972</v>
       </c>
       <c r="R12" t="n">
-        <v>6361219</v>
+        <v>6361201</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376264</v>
+        <v>121376330</v>
       </c>
       <c r="B13" t="n">
         <v>102320</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703994</v>
+        <v>703981</v>
       </c>
       <c r="R13" t="n">
-        <v>6361190</v>
+        <v>6361192</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376328</v>
+        <v>121376313</v>
       </c>
       <c r="B14" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,50 +2130,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703968</v>
+        <v>704129</v>
       </c>
       <c r="R14" t="n">
-        <v>6361190</v>
+        <v>6361185</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2203,11 +2194,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,7 +2225,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376327</v>
+        <v>121376264</v>
       </c>
       <c r="B15" t="n">
         <v>102320</v>
@@ -2274,7 +2260,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,7 +2270,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2293,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703972</v>
+        <v>703994</v>
       </c>
       <c r="R15" t="n">
-        <v>6361201</v>
+        <v>6361190</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2333,7 +2319,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>0,3- 0,6 m hög.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,10 +2351,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376315</v>
+        <v>121376325</v>
       </c>
       <c r="B16" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2377,41 +2363,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>704108</v>
+        <v>703973</v>
       </c>
       <c r="R16" t="n">
-        <v>6361297</v>
+        <v>6361219</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2441,6 +2441,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376313</v>
+        <v>121376328</v>
       </c>
       <c r="B17" t="n">
-        <v>108989</v>
+        <v>102320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,41 +2489,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704129</v>
+        <v>703968</v>
       </c>
       <c r="R17" t="n">
-        <v>6361185</v>
+        <v>6361190</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,6 +2562,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,10 +2598,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376331</v>
+        <v>121376320</v>
       </c>
       <c r="B18" t="n">
-        <v>102320</v>
+        <v>108989</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,55 +2610,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703981</v>
+        <v>704027</v>
       </c>
       <c r="R18" t="n">
-        <v>6361192</v>
+        <v>6361257</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2669,11 +2674,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2938,7 +2938,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376320</v>
+        <v>121376315</v>
       </c>
       <c r="B21" t="n">
         <v>108989</v>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704027</v>
+        <v>704108</v>
       </c>
       <c r="R21" t="n">
-        <v>6361257</v>
+        <v>6361297</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -3048,11 +3048,11 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -3048,7 +3048,7 @@
         <v>121391816</v>
       </c>
       <c r="B22" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16857438</v>
+        <v>161337</v>
       </c>
       <c r="B2" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41, Gtl</t>
+          <t>Lojsta haid, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704037.8697255934</v>
+        <v>704081</v>
       </c>
       <c r="R2" t="n">
-        <v>6361227.992736028</v>
+        <v>6361200</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,31 +765,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16857446</v>
+        <v>171715</v>
       </c>
       <c r="B3" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +797,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,14 +822,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41, Gtl</t>
+          <t>Lojsta haid, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703981.4977398629</v>
+        <v>704100</v>
       </c>
       <c r="R3" t="n">
-        <v>6361218.154135691</v>
+        <v>6361167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,31 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16857445</v>
+        <v>16857448</v>
       </c>
       <c r="B4" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,23 +904,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -966,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703954.2136625407</v>
+        <v>704026</v>
       </c>
       <c r="R4" t="n">
-        <v>6361200.578562107</v>
+        <v>6361220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,19 +966,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16857442</v>
+        <v>194336</v>
       </c>
       <c r="B5" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,43 +1006,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41, Gtl</t>
+          <t>Lojsta haid, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704109.2057574476</v>
+        <v>704057</v>
       </c>
       <c r="R5" t="n">
-        <v>6361241.821905858</v>
+        <v>6361204</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,22 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,31 +1085,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16857448</v>
+        <v>16857435</v>
       </c>
       <c r="B6" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,26 +1117,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704025.7946797023</v>
+        <v>704058</v>
       </c>
       <c r="R6" t="n">
-        <v>6361220.363908129</v>
+        <v>6361199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,19 +1183,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16857440</v>
+        <v>16857443</v>
       </c>
       <c r="B7" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,31 +1223,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232138</v>
+        <v>449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704037.8697255934</v>
+        <v>704099</v>
       </c>
       <c r="R7" t="n">
-        <v>6361227.992736028</v>
+        <v>6361207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,19 +1289,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,37 +1318,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16857439</v>
+        <v>16857445</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1441,7 +1353,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1450,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704037.8697255934</v>
+        <v>703954</v>
       </c>
       <c r="R8" t="n">
-        <v>6361227.992736028</v>
+        <v>6361201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,19 +1395,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16857447</v>
+        <v>16857437</v>
       </c>
       <c r="B9" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1459,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1571,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703981.4977398629</v>
+        <v>704058</v>
       </c>
       <c r="R9" t="n">
-        <v>6361218.154135691</v>
+        <v>6361199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,19 +1501,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,37 +1530,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16857441</v>
+        <v>16857439</v>
       </c>
       <c r="B10" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>232138</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1692,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704043.5204415806</v>
+        <v>704038</v>
       </c>
       <c r="R10" t="n">
-        <v>6361255.839575155</v>
+        <v>6361228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,19 +1607,9 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,50 +1636,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120639587</v>
+        <v>16857447</v>
       </c>
       <c r="B11" t="n">
-        <v>86174</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bojtel, Bojtel, Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703988</v>
+        <v>703981</v>
       </c>
       <c r="R11" t="n">
-        <v>6361183</v>
+        <v>6361218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,12 +1710,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,49 +1730,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121376331</v>
+        <v>16857433</v>
       </c>
       <c r="B12" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>3712</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1906,27 +1777,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703981</v>
+        <v>704098</v>
       </c>
       <c r="R12" t="n">
-        <v>6361192</v>
+        <v>6361176</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1950,17 +1816,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1,6 m hög.fertil, stam 1,5 cm i diameter.</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,88 +1832,73 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121376264</v>
+        <v>16857436</v>
       </c>
       <c r="B13" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703994</v>
+        <v>704058</v>
       </c>
       <c r="R13" t="n">
-        <v>6361190</v>
+        <v>6361199</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2076,17 +1922,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0,3- 0,6 m hög.</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,74 +1938,73 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121376320</v>
+        <v>16857446</v>
       </c>
       <c r="B14" t="n">
-        <v>108997</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>704027</v>
+        <v>703981</v>
       </c>
       <c r="R14" t="n">
-        <v>6361257</v>
+        <v>6361218</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2188,12 +2028,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,83 +2044,64 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121376328</v>
+        <v>121376313</v>
       </c>
       <c r="B15" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703968</v>
+        <v>704129</v>
       </c>
       <c r="R15" t="n">
-        <v>6361190</v>
+        <v>6361185</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2310,11 +2131,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,67 +2162,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121376325</v>
+        <v>121376315</v>
       </c>
       <c r="B16" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703973</v>
+        <v>704108</v>
       </c>
       <c r="R16" t="n">
-        <v>6361219</v>
+        <v>6361297</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2436,11 +2233,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,67 +2264,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121376323</v>
+        <v>121376317</v>
       </c>
       <c r="B17" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:41., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703993</v>
+        <v>704098</v>
       </c>
       <c r="R17" t="n">
-        <v>6361232</v>
+        <v>6361295</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2562,11 +2335,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,15 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121376317</v>
+        <v>121376320</v>
       </c>
       <c r="B18" t="n">
-        <v>108997</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704098</v>
+        <v>704027</v>
       </c>
       <c r="R18" t="n">
-        <v>6361295</v>
+        <v>6361257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,53 +2468,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121376313</v>
+        <v>16857440</v>
       </c>
       <c r="B19" t="n">
-        <v>108997</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>232138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704129</v>
+        <v>704038</v>
       </c>
       <c r="R19" t="n">
-        <v>6361185</v>
+        <v>6361228</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2775,12 +2542,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,36 +2558,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121376327</v>
+        <v>16857441</v>
       </c>
       <c r="B20" t="n">
-        <v>102328</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,51 +2585,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6037533</v>
+        <v>232138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703972</v>
+        <v>704044</v>
       </c>
       <c r="R20" t="n">
-        <v>6361201</v>
+        <v>6361256</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2896,17 +2648,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,74 +2664,73 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121376315</v>
+        <v>16857442</v>
       </c>
       <c r="B21" t="n">
-        <v>108997</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>232138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41., Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704108</v>
+        <v>704109</v>
       </c>
       <c r="R21" t="n">
-        <v>6361297</v>
+        <v>6361242</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3008,12 +2754,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3024,36 +2770,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121391816</v>
+        <v>16857444</v>
       </c>
       <c r="B22" t="n">
-        <v>102229</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3061,46 +2797,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6037533</v>
+        <v>232138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:41 vägförgrening 300–340 m N, grustag NV, Gtl</t>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>703987</v>
+        <v>703956</v>
       </c>
       <c r="R22" t="n">
-        <v>6361209</v>
+        <v>6361161</v>
       </c>
       <c r="S22" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3119,27 +2855,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Lojsta</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>I-Got-1581</t>
+          <t>Hejde</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 träd/plantor med koordinater 1655601 6360972 (6 m, 1,8 m, 2,3 m), 1655627 6360972 (6 plantor 0,3–0,6 m), 1655614 6360974 (1,8 m + 1,6 m), 1655605 6360983 (5,5 + 2 m), 1655606 6361001 (1,7 m), 1655626 6361014 (2,3 m)</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3154,15 +2880,1283 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16857438</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>704038</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6361228</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120639308</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bojtel, Bojtel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>704161</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6361193</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120639587</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bojtel, Bojtel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>703988</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6361183</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121376263</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>703994</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6361190</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>0,6 m hög.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121376311</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>704098</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6361181</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1,6 m hög.steril, 5 stammar alla 1 cm i diameter från avsågad stam 3,5 cm i diameter..</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121376323</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>703993</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6361232</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2,3 m hög.fertil, stam 1,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121376325</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>703973</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6361219</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1,7 m hög.steril, stam 1 cm i diameter från äldre rot.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121376327</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>703972</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6361201</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>5,5 m hög.fertil, stam 5 cm i diameter. + 2 m hög med 5 stammaralla 1 cm i diameter; avstånd 1 m mellan träden, möjligen från samma rot?</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121376328</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>703968</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6361190</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>6 m hög.fertil, stam 4,5 cm i diameter. + 1 tanig 1,8 m hög, steril. + 2,3 m hög, 2 stammar 1 + 1,5 cm i diameter, steril, från äldre rot2,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121376330</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>703981</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6361192</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1,8 m hög.angripen, stam 1,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121391816</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:41 vägförgrening 300–340 m N, grustag NV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>703987</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6361209</v>
+      </c>
+      <c r="S33" t="n">
+        <v>31</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>I-Got-1581</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>15 träd/plantor med koordinater 1655601 6360972 (6 m, 1,8 m, 2,3 m), 1655627 6360972 (6 plantor 0,3–0,6 m), 1655614 6360974 (1,8 m + 1,6 m), 1655605 6360983 (5,5 + 2 m), 1655606 6361001 (1,7 m), 1655626 6361014 (2,3 m)</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Bengt Carlsson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Jörgen Petersson, Gun Ingmansson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -3205,7 +3205,7 @@
         <v>121376263</v>
       </c>
       <c r="B26" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>121376311</v>
       </c>
       <c r="B27" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>121376323</v>
       </c>
       <c r="B28" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>121376325</v>
       </c>
       <c r="B29" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>121376327</v>
       </c>
       <c r="B30" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>121376328</v>
       </c>
       <c r="B31" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>121376330</v>
       </c>
       <c r="B32" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>121391816</v>
       </c>
       <c r="B33" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 2649-2023 artfynd.xlsx
+++ b/artfynd/A 2649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/171715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857448</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857435</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857443</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857445</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857437</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857439</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857433</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857436</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857446</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2159,6 +2229,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376313</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376315</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2363,6 +2443,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376320</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2571,6 +2661,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857440</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2677,6 +2772,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857441</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857442</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857444</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16857438</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3102,6 +3217,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639308</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3199,6 +3319,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639587</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3320,6 +3445,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376263</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3441,6 +3571,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376311</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,6 +3697,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376323</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3683,6 +3823,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376325</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3804,6 +3949,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376327</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3920,6 +4070,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376328</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4041,6 +4196,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376330</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4161,8 +4321,47 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121391816</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>